--- a/data/trans_camb/P1802_2016_2023-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1802_2016_2023-Provincia-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>9,76</t>
+          <t>7,37</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13,8</t>
+          <t>12,16</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,64</t>
+          <t>9,77</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 17,4</t>
+          <t>-0,03; 14,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 20,61</t>
+          <t>4,71; 18,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,32; 17,04</t>
+          <t>4,89; 14,7</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>42,49%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,3; 95,93</t>
+          <t>-0,72; 84,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,52; 98,06</t>
+          <t>14,65; 86,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,13; 82,72</t>
+          <t>19,08; 72,88</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-4,91</t>
+          <t>-4,57</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-2,12</t>
+          <t>-2,39</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,57</t>
+          <t>-3,48</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -0,54</t>
+          <t>-8,79; -0,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 2,9</t>
+          <t>-7,03; 2,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,28; -0,53</t>
+          <t>-6,63; -0,1</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-31,63%</t>
+          <t>-29,42%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-10,9%</t>
+          <t>-12,32%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-20,4%</t>
+          <t>-19,88%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,07; -3,67</t>
+          <t>-49,69; -0,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,96; 17,36</t>
+          <t>-32,06; 13,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,89; -2,51</t>
+          <t>-34,49; -0,82</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14,73</t>
+          <t>14,8</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16,3</t>
+          <t>16,35</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15,58</t>
+          <t>15,66</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,78; 19,92</t>
+          <t>10,29; 20,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,95; 21,18</t>
+          <t>11,48; 21,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,73; 19,21</t>
+          <t>12,25; 19,39</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>196,74%</t>
+          <t>197,69%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>164,31%</t>
+          <t>164,81%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>178,35%</t>
+          <t>179,27%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>99,19; 375,22</t>
+          <t>104,35; 390,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>78,88; 281,89</t>
+          <t>87,66; 296,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>109,5; 276,49</t>
+          <t>111,41; 270,8</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-2,4</t>
+          <t>-4,54</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-10,81</t>
+          <t>-7,74</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-7,18</t>
+          <t>-6,18</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 4,34</t>
+          <t>-10,02; 1,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,31; -4,76</t>
+          <t>-13,12; -2,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,63; -3,17</t>
+          <t>-10,23; -2,13</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-12,74%</t>
+          <t>-24,07%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-48,86%</t>
+          <t>-35,01%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-34,95%</t>
+          <t>-30,09%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,81; 25,97</t>
+          <t>-48,15; 10,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-69,92; -28,32</t>
+          <t>-50,3; -12,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,87; -16,39</t>
+          <t>-44,72; -11,86</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-5,79</t>
+          <t>-6,96</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-12,77</t>
+          <t>-12,82</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-9,56</t>
+          <t>-10,05</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 1,17</t>
+          <t>-13,97; 0,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,59; -7,67</t>
+          <t>-18,39; -7,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,27; -4,91</t>
+          <t>-14,5; -6,03</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-30,94%</t>
+          <t>-37,22%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-69,55%</t>
+          <t>-69,83%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-51,58%</t>
+          <t>-54,2%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-57,07; 9,61</t>
+          <t>-60,26; 1,9</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-80,5; -52,23</t>
+          <t>-81,29; -52,51</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-65,03; -29,92</t>
+          <t>-67,18; -37,19</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3,85</t>
+          <t>3,38</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-0,72</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>1,25</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 9,52</t>
+          <t>-2,92; 9,04</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 5,24</t>
+          <t>-7,24; 5,39</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 5,57</t>
+          <t>-3,46; 5,45</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-2,97%</t>
+          <t>-3,53%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 93,03</t>
+          <t>-18,1; 82,73</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 31,28</t>
+          <t>-28,05; 32,77</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 38,52</t>
+          <t>-18,18; 36,85</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>9,86</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>10,33</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>3,08</t>
-        </is>
-      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6,55</t>
+          <t>10,14</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,97; 14,64</t>
+          <t>5,86; 14,01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 10,5</t>
+          <t>5,88; 14,59</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 10,72</t>
+          <t>7,19; 12,92</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>100,55%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>75,04%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>48,3; 167,09</t>
+          <t>48,74; 168,7</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-46,73; 65,94</t>
+          <t>29,76; 103,67</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 84,55</t>
+          <t>47,9; 108,25</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>16,39</t>
+          <t>-8,44</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-12,75</t>
+          <t>-12,51</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3,27</t>
+          <t>-10,54</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 54,51</t>
+          <t>-11,6; -4,97</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-16,2; -9,48</t>
+          <t>-16,21; -9,29</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 33,74</t>
+          <t>-12,92; -8,21</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>112,75%</t>
+          <t>-58,02%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-64,13%</t>
+          <t>-62,9%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>-60,94%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-61,43; 445,03</t>
+          <t>-69,69; -39,01</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-72,53; -53,35</t>
+          <t>-71,84; -51,27</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 204,58</t>
+          <t>-68,72; -51,52</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>7,51</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-1,7</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>0,31</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,02; 25,54</t>
+          <t>-0,88; 2,57</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 0,43</t>
+          <t>-1,81; 1,54</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 13,81</t>
+          <t>-1,02; 1,48</t>
         </is>
       </c>
     </row>
@@ -1362,17 +1362,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-8,99%</t>
+          <t>-0,7%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>7,26; 187,07</t>
+          <t>-5,78; 18,89</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-24,92; 2,33</t>
+          <t>-9,08; 8,54</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 86,93</t>
+          <t>-5,73; 9,3</t>
         </is>
       </c>
     </row>
